--- a/dataset_t6_grouped/results2/G4/G4_T3211_W0021F0001T0006Z000C1N5_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T3211_W0021F0001T0006Z000C1N5_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>38.22171940421271</v>
+        <v>6.211029403184567</v>
       </c>
       <c r="D2" t="n">
-        <v>37.89433692560455</v>
+        <v>6.157829750410739</v>
       </c>
       <c r="E2" t="n">
-        <v>17.61426798718178</v>
+        <v>2.862318547917039</v>
       </c>
       <c r="F2" t="n">
-        <v>14.32283576094758</v>
+        <v>2.327460811153982</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>48.072224574178</v>
+        <v>7.811736493303925</v>
       </c>
       <c r="D3" t="n">
-        <v>19.47434209415045</v>
+        <v>3.164580590299448</v>
       </c>
       <c r="E3" t="n">
-        <v>17.61426798718178</v>
+        <v>2.862318547917039</v>
       </c>
       <c r="F3" t="n">
-        <v>14.32283576094758</v>
+        <v>2.327460811153982</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>16.52509199515168</v>
+        <v>2.685327449212148</v>
       </c>
       <c r="D4" t="n">
-        <v>16.03779070261429</v>
+        <v>2.606140989174822</v>
       </c>
       <c r="E4" t="n">
-        <v>17.61426798718178</v>
+        <v>2.862318547917039</v>
       </c>
       <c r="F4" t="n">
-        <v>14.32283576094758</v>
+        <v>2.327460811153982</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>54.14090204991189</v>
+        <v>8.797896583110681</v>
       </c>
       <c r="D5" t="n">
-        <v>11.55999783791491</v>
+        <v>1.878499648661172</v>
       </c>
       <c r="E5" t="n">
-        <v>17.61426798718178</v>
+        <v>2.862318547917039</v>
       </c>
       <c r="F5" t="n">
-        <v>14.32283576094758</v>
+        <v>2.327460811153982</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>11.2254266770414</v>
+        <v>1.824131835019228</v>
       </c>
       <c r="D6" t="n">
-        <v>52.28029441930021</v>
+        <v>8.495547843136285</v>
       </c>
       <c r="E6" t="n">
-        <v>17.61426798718178</v>
+        <v>2.862318547917039</v>
       </c>
       <c r="F6" t="n">
-        <v>14.32283576094758</v>
+        <v>2.327460811153982</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>11.27621661837381</v>
+        <v>1.832385200485744</v>
       </c>
       <c r="D7" t="n">
-        <v>35.85593866763534</v>
+        <v>5.826590033490742</v>
       </c>
       <c r="E7" t="n">
-        <v>17.61426798718178</v>
+        <v>2.862318547917039</v>
       </c>
       <c r="F7" t="n">
-        <v>14.32283576094758</v>
+        <v>2.327460811153982</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
